--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importLocalEquipmentSupply.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importLocalEquipmentSupply.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27260" windowHeight="11920"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
+    <sheet name="属地设备供应情况" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -36,10 +36,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -62,32 +62,49 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -99,9 +116,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,16 +146,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,9 +192,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,60 +208,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,49 +228,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,133 +384,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,11 +437,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -457,15 +496,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -487,45 +517,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -534,153 +525,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importLocalEquipmentSupply.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importLocalEquipmentSupply.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27260" windowHeight="11920"/>
+    <workbookView windowWidth="27260" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="属地设备供应情况" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -36,10 +36,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -63,6 +63,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -71,24 +78,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -100,9 +100,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,98 +161,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,19 +240,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,145 +402,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,17 +437,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -457,15 +451,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -485,17 +470,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -515,6 +494,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -526,11 +520,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -539,148 +539,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1044,6 +1044,11 @@
       <c r="E2" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数字格式错误！" sqref="D$1:D$1048576">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importLocalEquipmentSupply.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importLocalEquipmentSupply.xlsx
@@ -35,11 +35,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="0.0000_);\(0.0000\)"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -63,19 +64,19 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -84,9 +85,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -100,38 +107,64 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -145,62 +178,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,19 +235,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -258,13 +385,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -276,139 +397,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,8 +441,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -450,7 +466,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -472,9 +503,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -493,205 +535,173 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1016,32 +1026,34 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="16.7211538461538" customWidth="1"/>
+    <col min="1" max="3" width="16.7211538461538" customWidth="1"/>
+    <col min="4" max="4" width="16.7211538461538" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7211538461538" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:5">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
